--- a/data-manipulation-scripts/sheets-cleanup/sheets/CARCAÇA EXTERNA EMBREAGEM.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CARCAÇA EXTERNA EMBREAGEM.xlsx
@@ -28,25 +28,25 @@
     <t>618341655775</t>
   </si>
   <si>
-    <t>CARCAÇA EXTERNA EMBREAGEM IRON CG TITAN 2000 A 2004 KS/ FAN125 2005 A 2008 201217</t>
+    <t xml:space="preserve">CAMPANA EXTERNA EMBREAGEM IRON CG TITAN 2000 A 2004 KS/ FAN125 2005 A 2008 201217 </t>
   </si>
   <si>
     <t>618341655782</t>
   </si>
   <si>
-    <t>CARCAÇA EXTERNA EMBREAGEM IRON FAN TITAN160/ START/ BROS NXR160 2015 201215</t>
+    <t>CAMPANA EXTERNA EMBREAGEM IRON FAN TITAN160/ START/ BROS NXR160 2015 201215</t>
   </si>
   <si>
     <t>7908073718507</t>
   </si>
   <si>
-    <t>CARCAÇA EXTERNA EMBREAGEM SMARTFOX FAZER150/ XTZ150/ FACTOR150</t>
+    <t>CAMPANA EXTERNA EMBREAGEM SMARTFOX FAZER150/ XTZ150/ FACTOR150</t>
   </si>
   <si>
     <t>618341655805</t>
   </si>
   <si>
-    <t>CARCAÇA EXTERNA EMBREAGEM IRON CG TITAN150 200 A 2008 KS/ BROS NXR150 2006 A 2014/ FAN125 2009 2013 201211</t>
+    <t>CAMPANA EXTERNA EMBREAGEM IRON CG TITAN150 200 A 2008 KS/ BROS NXR150 2006 A 2014/ FAN125 2009 2013 201211</t>
   </si>
 </sst>
 </file>
@@ -104,10 +104,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -374,10 +374,12 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>2.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>230.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -408,10 +410,10 @@
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>1.0</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="5">
         <v>210.0</v>
       </c>
       <c r="E3" s="6"/>
@@ -444,10 +446,12 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>1.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="4">
+        <v>360.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -475,7 +479,7 @@
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="7">
